--- a/artfynd/A 16829-2026 artfynd.xlsx
+++ b/artfynd/A 16829-2026 artfynd.xlsx
@@ -1480,12 +1480,7 @@
         <v>113680579</v>
       </c>
       <c r="B9" t="n">
-        <v>91649</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,19 +1492,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1577,12 +1568,12 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1591,12 +1582,7 @@
         <v>113680577</v>
       </c>
       <c r="B10" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93184</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,12 +1674,12 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1702,12 +1688,7 @@
         <v>113679200</v>
       </c>
       <c r="B11" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79342</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,12 +1780,12 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1813,12 +1794,7 @@
         <v>113679201</v>
       </c>
       <c r="B12" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79342</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,12 +1886,12 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1924,12 +1900,7 @@
         <v>113680704</v>
       </c>
       <c r="B13" t="n">
-        <v>91623</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93190</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,12 +1992,12 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2035,12 +2006,7 @@
         <v>113680578</v>
       </c>
       <c r="B14" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93184</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,12 +2098,12 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2146,12 +2112,7 @@
         <v>113680703</v>
       </c>
       <c r="B15" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93172</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,12 +2204,12 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2257,12 +2218,7 @@
         <v>113680576</v>
       </c>
       <c r="B16" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93172</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,12 +2310,12 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2368,12 +2324,7 @@
         <v>113679202</v>
       </c>
       <c r="B17" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79067</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,12 +2416,12 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2479,12 +2430,7 @@
         <v>113680575</v>
       </c>
       <c r="B18" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93172</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2576,12 +2522,12 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2590,12 +2536,7 @@
         <v>113680699</v>
       </c>
       <c r="B19" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93184</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2687,12 +2628,12 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2701,12 +2642,7 @@
         <v>113682624</v>
       </c>
       <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,12 +2747,12 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2825,12 +2761,7 @@
         <v>113682663</v>
       </c>
       <c r="B21" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,12 +2866,12 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2949,12 +2880,7 @@
         <v>113682665</v>
       </c>
       <c r="B22" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,12 +2985,12 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3073,12 +2999,7 @@
         <v>113682662</v>
       </c>
       <c r="B23" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,12 +3104,12 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3197,12 +3118,7 @@
         <v>113682670</v>
       </c>
       <c r="B24" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3307,12 +3223,12 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3321,12 +3237,7 @@
         <v>113682668</v>
       </c>
       <c r="B25" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3431,12 +3342,12 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3445,12 +3356,7 @@
         <v>113682669</v>
       </c>
       <c r="B26" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3555,12 +3461,12 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3569,12 +3475,7 @@
         <v>113682667</v>
       </c>
       <c r="B27" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3679,12 +3580,12 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3693,12 +3594,7 @@
         <v>113682623</v>
       </c>
       <c r="B28" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3803,12 +3699,12 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3817,12 +3713,7 @@
         <v>113682666</v>
       </c>
       <c r="B29" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3927,12 +3818,12 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3941,12 +3832,7 @@
         <v>113682664</v>
       </c>
       <c r="B30" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4051,12 +3937,12 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 16829-2026 artfynd.xlsx
+++ b/artfynd/A 16829-2026 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>113680579</v>
       </c>
       <c r="B9" t="n">
-        <v>93206</v>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>113680577</v>
       </c>
       <c r="B10" t="n">
-        <v>93189</v>
+        <v>93192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>113679200</v>
       </c>
       <c r="B11" t="n">
-        <v>79347</v>
+        <v>79349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>113679201</v>
       </c>
       <c r="B12" t="n">
-        <v>79347</v>
+        <v>79349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>113680704</v>
       </c>
       <c r="B13" t="n">
-        <v>93195</v>
+        <v>93198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>113680578</v>
       </c>
       <c r="B14" t="n">
-        <v>93189</v>
+        <v>93192</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>113680703</v>
       </c>
       <c r="B15" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>113680576</v>
       </c>
       <c r="B16" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>113679202</v>
       </c>
       <c r="B17" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>113680575</v>
       </c>
       <c r="B18" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>113680699</v>
       </c>
       <c r="B19" t="n">
-        <v>93189</v>
+        <v>93192</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>113682624</v>
       </c>
       <c r="B20" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>113682663</v>
       </c>
       <c r="B21" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>113682665</v>
       </c>
       <c r="B22" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>113682662</v>
       </c>
       <c r="B23" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>113682670</v>
       </c>
       <c r="B24" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>113682668</v>
       </c>
       <c r="B25" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>113682669</v>
       </c>
       <c r="B26" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>113682667</v>
       </c>
       <c r="B27" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>113682623</v>
       </c>
       <c r="B28" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>113682666</v>
       </c>
       <c r="B29" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>113682664</v>
       </c>
       <c r="B30" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16829-2026 artfynd.xlsx
+++ b/artfynd/A 16829-2026 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>113680579</v>
       </c>
       <c r="B9" t="n">
-        <v>93209</v>
+        <v>93215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>113680577</v>
       </c>
       <c r="B10" t="n">
-        <v>93192</v>
+        <v>93198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>113679200</v>
       </c>
       <c r="B11" t="n">
-        <v>79349</v>
+        <v>79351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>113679201</v>
       </c>
       <c r="B12" t="n">
-        <v>79349</v>
+        <v>79351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>113680704</v>
       </c>
       <c r="B13" t="n">
-        <v>93198</v>
+        <v>93204</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>113680578</v>
       </c>
       <c r="B14" t="n">
-        <v>93192</v>
+        <v>93198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>113680703</v>
       </c>
       <c r="B15" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>113680576</v>
       </c>
       <c r="B16" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>113679202</v>
       </c>
       <c r="B17" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>113680575</v>
       </c>
       <c r="B18" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>113680699</v>
       </c>
       <c r="B19" t="n">
-        <v>93192</v>
+        <v>93198</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>113682624</v>
       </c>
       <c r="B20" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>113682663</v>
       </c>
       <c r="B21" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>113682665</v>
       </c>
       <c r="B22" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>113682662</v>
       </c>
       <c r="B23" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>113682670</v>
       </c>
       <c r="B24" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>113682668</v>
       </c>
       <c r="B25" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>113682669</v>
       </c>
       <c r="B26" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>113682667</v>
       </c>
       <c r="B27" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>113682623</v>
       </c>
       <c r="B28" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>113682666</v>
       </c>
       <c r="B29" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>113682664</v>
       </c>
       <c r="B30" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16829-2026 artfynd.xlsx
+++ b/artfynd/A 16829-2026 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>113680579</v>
       </c>
       <c r="B9" t="n">
-        <v>93215</v>
+        <v>93225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>113680577</v>
       </c>
       <c r="B10" t="n">
-        <v>93198</v>
+        <v>93208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>113679200</v>
       </c>
       <c r="B11" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>113679201</v>
       </c>
       <c r="B12" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>113680704</v>
       </c>
       <c r="B13" t="n">
-        <v>93204</v>
+        <v>93214</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>113680578</v>
       </c>
       <c r="B14" t="n">
-        <v>93198</v>
+        <v>93208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>113680703</v>
       </c>
       <c r="B15" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>113680576</v>
       </c>
       <c r="B16" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>113679202</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>113680575</v>
       </c>
       <c r="B18" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>113680699</v>
       </c>
       <c r="B19" t="n">
-        <v>93198</v>
+        <v>93208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>113682624</v>
       </c>
       <c r="B20" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>113682663</v>
       </c>
       <c r="B21" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>113682665</v>
       </c>
       <c r="B22" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>113682662</v>
       </c>
       <c r="B23" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>113682670</v>
       </c>
       <c r="B24" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>113682668</v>
       </c>
       <c r="B25" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>113682669</v>
       </c>
       <c r="B26" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>113682667</v>
       </c>
       <c r="B27" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>113682623</v>
       </c>
       <c r="B28" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>113682666</v>
       </c>
       <c r="B29" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>113682664</v>
       </c>
       <c r="B30" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16829-2026 artfynd.xlsx
+++ b/artfynd/A 16829-2026 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>113680579</v>
       </c>
       <c r="B9" t="n">
-        <v>93225</v>
+        <v>93226</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>113680577</v>
       </c>
       <c r="B10" t="n">
-        <v>93208</v>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>113680704</v>
       </c>
       <c r="B13" t="n">
-        <v>93214</v>
+        <v>93215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>113680578</v>
       </c>
       <c r="B14" t="n">
-        <v>93208</v>
+        <v>93209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>113680703</v>
       </c>
       <c r="B15" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>113680576</v>
       </c>
       <c r="B16" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>113680575</v>
       </c>
       <c r="B18" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>113680699</v>
       </c>
       <c r="B19" t="n">
-        <v>93208</v>
+        <v>93209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>113682624</v>
       </c>
       <c r="B20" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>113682663</v>
       </c>
       <c r="B21" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>113682665</v>
       </c>
       <c r="B22" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>113682662</v>
       </c>
       <c r="B23" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>113682670</v>
       </c>
       <c r="B24" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>113682668</v>
       </c>
       <c r="B25" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>113682669</v>
       </c>
       <c r="B26" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>113682667</v>
       </c>
       <c r="B27" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>113682623</v>
       </c>
       <c r="B28" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>113682666</v>
       </c>
       <c r="B29" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>113682664</v>
       </c>
       <c r="B30" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16829-2026 artfynd.xlsx
+++ b/artfynd/A 16829-2026 artfynd.xlsx
@@ -2642,7 +2642,7 @@
         <v>113682624</v>
       </c>
       <c r="B20" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>113682663</v>
       </c>
       <c r="B21" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>113682665</v>
       </c>
       <c r="B22" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>113682662</v>
       </c>
       <c r="B23" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>113682670</v>
       </c>
       <c r="B24" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>113682668</v>
       </c>
       <c r="B25" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>113682669</v>
       </c>
       <c r="B26" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>113682667</v>
       </c>
       <c r="B27" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>113682623</v>
       </c>
       <c r="B28" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>113682666</v>
       </c>
       <c r="B29" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>113682664</v>
       </c>
       <c r="B30" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16829-2026 artfynd.xlsx
+++ b/artfynd/A 16829-2026 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>113680579</v>
       </c>
       <c r="B9" t="n">
-        <v>93226</v>
+        <v>93227</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>113680577</v>
       </c>
       <c r="B10" t="n">
-        <v>93209</v>
+        <v>93210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>113679200</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>113679201</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>113680704</v>
       </c>
       <c r="B13" t="n">
-        <v>93215</v>
+        <v>93216</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>113680578</v>
       </c>
       <c r="B14" t="n">
-        <v>93209</v>
+        <v>93210</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>113680703</v>
       </c>
       <c r="B15" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>113680576</v>
       </c>
       <c r="B16" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>113679202</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>113680575</v>
       </c>
       <c r="B18" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>113680699</v>
       </c>
       <c r="B19" t="n">
-        <v>93209</v>
+        <v>93210</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>113682624</v>
       </c>
       <c r="B20" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>113682663</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>113682665</v>
       </c>
       <c r="B22" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>113682662</v>
       </c>
       <c r="B23" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>113682670</v>
       </c>
       <c r="B24" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>113682668</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>113682669</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>113682667</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>113682623</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>113682666</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>113682664</v>
       </c>
       <c r="B30" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16829-2026 artfynd.xlsx
+++ b/artfynd/A 16829-2026 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>113680579</v>
       </c>
       <c r="B9" t="n">
-        <v>93227</v>
+        <v>93229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>113680577</v>
       </c>
       <c r="B10" t="n">
-        <v>93210</v>
+        <v>93212</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>113680704</v>
       </c>
       <c r="B13" t="n">
-        <v>93216</v>
+        <v>93218</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>113680578</v>
       </c>
       <c r="B14" t="n">
-        <v>93210</v>
+        <v>93212</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>113680703</v>
       </c>
       <c r="B15" t="n">
-        <v>93198</v>
+        <v>93200</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>113680576</v>
       </c>
       <c r="B16" t="n">
-        <v>93198</v>
+        <v>93200</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>113680575</v>
       </c>
       <c r="B18" t="n">
-        <v>93198</v>
+        <v>93200</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>113680699</v>
       </c>
       <c r="B19" t="n">
-        <v>93210</v>
+        <v>93212</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>113682624</v>
       </c>
       <c r="B20" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>113682663</v>
       </c>
       <c r="B21" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>113682665</v>
       </c>
       <c r="B22" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>113682662</v>
       </c>
       <c r="B23" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>113682670</v>
       </c>
       <c r="B24" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>113682668</v>
       </c>
       <c r="B25" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>113682669</v>
       </c>
       <c r="B26" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>113682667</v>
       </c>
       <c r="B27" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>113682623</v>
       </c>
       <c r="B28" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>113682666</v>
       </c>
       <c r="B29" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>113682664</v>
       </c>
       <c r="B30" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16829-2026 artfynd.xlsx
+++ b/artfynd/A 16829-2026 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>113680579</v>
       </c>
       <c r="B9" t="n">
-        <v>93229</v>
+        <v>93230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>113680577</v>
       </c>
       <c r="B10" t="n">
-        <v>93212</v>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>113679200</v>
       </c>
       <c r="B11" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>113679201</v>
       </c>
       <c r="B12" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>113680704</v>
       </c>
       <c r="B13" t="n">
-        <v>93218</v>
+        <v>93219</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>113680578</v>
       </c>
       <c r="B14" t="n">
-        <v>93212</v>
+        <v>93213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>113680703</v>
       </c>
       <c r="B15" t="n">
-        <v>93200</v>
+        <v>93201</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>113680576</v>
       </c>
       <c r="B16" t="n">
-        <v>93200</v>
+        <v>93201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>113679202</v>
       </c>
       <c r="B17" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>113680575</v>
       </c>
       <c r="B18" t="n">
-        <v>93200</v>
+        <v>93201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>113680699</v>
       </c>
       <c r="B19" t="n">
-        <v>93212</v>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>113682624</v>
       </c>
       <c r="B20" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>113682663</v>
       </c>
       <c r="B21" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>113682665</v>
       </c>
       <c r="B22" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>113682662</v>
       </c>
       <c r="B23" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>113682670</v>
       </c>
       <c r="B24" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>113682668</v>
       </c>
       <c r="B25" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>113682669</v>
       </c>
       <c r="B26" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>113682667</v>
       </c>
       <c r="B27" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>113682623</v>
       </c>
       <c r="B28" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>113682666</v>
       </c>
       <c r="B29" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>113682664</v>
       </c>
       <c r="B30" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16829-2026 artfynd.xlsx
+++ b/artfynd/A 16829-2026 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>113680579</v>
       </c>
       <c r="B9" t="n">
-        <v>93230</v>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>113680577</v>
       </c>
       <c r="B10" t="n">
-        <v>93213</v>
+        <v>93216</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>113679200</v>
       </c>
       <c r="B11" t="n">
-        <v>79361</v>
+        <v>79364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>113679201</v>
       </c>
       <c r="B12" t="n">
-        <v>79361</v>
+        <v>79364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>113680704</v>
       </c>
       <c r="B13" t="n">
-        <v>93219</v>
+        <v>93222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>113680578</v>
       </c>
       <c r="B14" t="n">
-        <v>93213</v>
+        <v>93216</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>113680703</v>
       </c>
       <c r="B15" t="n">
-        <v>93201</v>
+        <v>93204</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>113680576</v>
       </c>
       <c r="B16" t="n">
-        <v>93201</v>
+        <v>93204</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>113679202</v>
       </c>
       <c r="B17" t="n">
-        <v>79086</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>113680575</v>
       </c>
       <c r="B18" t="n">
-        <v>93201</v>
+        <v>93204</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>113680699</v>
       </c>
       <c r="B19" t="n">
-        <v>93213</v>
+        <v>93216</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>113682624</v>
       </c>
       <c r="B20" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>113682663</v>
       </c>
       <c r="B21" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>113682665</v>
       </c>
       <c r="B22" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>113682662</v>
       </c>
       <c r="B23" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>113682670</v>
       </c>
       <c r="B24" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>113682668</v>
       </c>
       <c r="B25" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>113682669</v>
       </c>
       <c r="B26" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>113682667</v>
       </c>
       <c r="B27" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>113682623</v>
       </c>
       <c r="B28" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>113682666</v>
       </c>
       <c r="B29" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>113682664</v>
       </c>
       <c r="B30" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16829-2026 artfynd.xlsx
+++ b/artfynd/A 16829-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>163096</v>
+        <v>163095</v>
       </c>
       <c r="B2" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584392.715091627</v>
+        <v>584454</v>
       </c>
       <c r="R2" t="n">
-        <v>6869803.791579572</v>
+        <v>6869571</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2012-05-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-05-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>163097</v>
+        <v>163096</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584391.9635039478</v>
+        <v>584393</v>
       </c>
       <c r="R3" t="n">
-        <v>6869624.884029775</v>
+        <v>6869804</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2012-05-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-05-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>163095</v>
+        <v>163097</v>
       </c>
       <c r="B4" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584453.6521576721</v>
+        <v>584392</v>
       </c>
       <c r="R4" t="n">
-        <v>6869570.86192351</v>
+        <v>6869625</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,19 +937,9 @@
           <t>2012-05-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-05-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1863887</v>
+        <v>113679200</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gråsjöberget etc, Hls</t>
+          <t>Bläckmyran, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584392.715091627</v>
+        <v>584415</v>
       </c>
       <c r="R5" t="n">
-        <v>6869803.791579572</v>
+        <v>6869734</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-05-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-05-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,31 +1047,35 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1979226</v>
+        <v>113679201</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,37 +1083,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gråsjöberget etc, Hls</t>
+          <t>Bläckmyran, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584276.2428135432</v>
+        <v>584403</v>
       </c>
       <c r="R6" t="n">
-        <v>6869671.448510909</v>
+        <v>6869732</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1137,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-05-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-05-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,31 +1153,35 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1979225</v>
+        <v>113680575</v>
       </c>
       <c r="B7" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,37 +1189,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gråsjöberget etc, Hls</t>
+          <t>Bläckmyran, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584280.289810131</v>
+        <v>584326</v>
       </c>
       <c r="R7" t="n">
-        <v>6869736.513683463</v>
+        <v>6869734</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1243,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-05-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-05-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,79 +1261,71 @@
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101356237</v>
+        <v>113680576</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>O Bläckmyran, Hls</t>
+          <t>Bläckmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584454.8221744534</v>
+        <v>584350</v>
       </c>
       <c r="R8" t="n">
-        <v>6869637.741128645</v>
+        <v>6869795</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,27 +1349,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spritt inom hänsynsytan</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,14 +1363,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1473,14 +1382,18 @@
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113680579</v>
+        <v>113680703</v>
       </c>
       <c r="B9" t="n">
-        <v>93233</v>
+        <v>93271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,19 +1401,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1508,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584499</v>
+        <v>584312</v>
       </c>
       <c r="R9" t="n">
-        <v>6869796</v>
+        <v>6869797</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,12 +1455,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,11 +1499,11 @@
         <v>113680577</v>
       </c>
       <c r="B10" t="n">
-        <v>93216</v>
+        <v>93283</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1685,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113679200</v>
+        <v>113680578</v>
       </c>
       <c r="B11" t="n">
-        <v>79364</v>
+        <v>93283</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1720,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584415</v>
+        <v>584424</v>
       </c>
       <c r="R11" t="n">
-        <v>6869734</v>
+        <v>6869780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,12 +1684,12 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW11" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1791,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113679201</v>
+        <v>113680699</v>
       </c>
       <c r="B12" t="n">
-        <v>79364</v>
+        <v>93283</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1719,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1826,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584403</v>
+        <v>584485</v>
       </c>
       <c r="R12" t="n">
-        <v>6869732</v>
+        <v>6869804</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1856,12 +1773,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,12 +1790,12 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW12" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1900,7 +1817,7 @@
         <v>113680704</v>
       </c>
       <c r="B13" t="n">
-        <v>93222</v>
+        <v>93289</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113680578</v>
+        <v>113680579</v>
       </c>
       <c r="B14" t="n">
-        <v>93216</v>
+        <v>93300</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,23 +1931,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Banker</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2038,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584424</v>
+        <v>584499</v>
       </c>
       <c r="R14" t="n">
-        <v>6869780</v>
+        <v>6869796</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,48 +2022,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113680703</v>
+        <v>1863887</v>
       </c>
       <c r="B15" t="n">
-        <v>93204</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bläckmyran, Hls</t>
+          <t>Gråsjöberget etc, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584312</v>
+        <v>584393</v>
       </c>
       <c r="R15" t="n">
-        <v>6869797</v>
+        <v>6869804</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2174,12 +2087,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2012-05-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2012-05-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,55 +2105,46 @@
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113680576</v>
+        <v>113679243</v>
       </c>
       <c r="B16" t="n">
-        <v>93204</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2250,10 +2154,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584350</v>
+        <v>584480</v>
       </c>
       <c r="R16" t="n">
-        <v>6869795</v>
+        <v>6869828</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,12 +2184,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,12 +2201,12 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW16" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2321,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113679202</v>
+        <v>1979225</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,17 +2256,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bläckmyran, Hls</t>
+          <t>Gråsjöberget etc, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584351</v>
+        <v>584280</v>
       </c>
       <c r="R17" t="n">
-        <v>6869755</v>
+        <v>6869737</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2386,12 +2290,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2012-05-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2012-05-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,73 +2306,64 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113680575</v>
+        <v>1979226</v>
       </c>
       <c r="B18" t="n">
-        <v>93204</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bläckmyran, Hls</t>
+          <t>Gråsjöberget etc, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584326</v>
+        <v>584276</v>
       </c>
       <c r="R18" t="n">
-        <v>6869734</v>
+        <v>6869671</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2492,12 +2387,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2012-05-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2012-05-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2510,55 +2405,46 @@
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113680699</v>
+        <v>113679202</v>
       </c>
       <c r="B19" t="n">
-        <v>93216</v>
+        <v>79130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2568,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584485</v>
+        <v>584351</v>
       </c>
       <c r="R19" t="n">
-        <v>6869804</v>
+        <v>6869755</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,12 +2484,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,12 +2501,12 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW19" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2639,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113682624</v>
+        <v>101356237</v>
       </c>
       <c r="B20" t="n">
-        <v>99125</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2682,17 +2568,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bläckmyran, Hls</t>
+          <t>O Bläckmyran, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584378</v>
+        <v>584455</v>
       </c>
       <c r="R20" t="n">
-        <v>6869797</v>
+        <v>6869638</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2716,12 +2602,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2022-05-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spritt inom hänsynsytan</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2734,15 +2625,10 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2750,18 +2636,14 @@
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113682663</v>
+        <v>113682623</v>
       </c>
       <c r="B21" t="n">
-        <v>99125</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2670,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2805,10 +2687,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584312</v>
+        <v>584365</v>
       </c>
       <c r="R21" t="n">
-        <v>6869573</v>
+        <v>6869805</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2835,12 +2717,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,10 +2759,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113682665</v>
+        <v>113682624</v>
       </c>
       <c r="B22" t="n">
-        <v>99125</v>
+        <v>99195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2924,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584312</v>
+        <v>584378</v>
       </c>
       <c r="R22" t="n">
-        <v>6869550</v>
+        <v>6869797</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2954,12 +2836,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,7 +2881,7 @@
         <v>113682662</v>
       </c>
       <c r="B23" t="n">
-        <v>99125</v>
+        <v>99195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,10 +2997,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113682670</v>
+        <v>113682663</v>
       </c>
       <c r="B24" t="n">
-        <v>99125</v>
+        <v>99195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3027,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3158,14 +3040,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storåsen, Hls</t>
+          <t>Bläckmyran, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584443</v>
+        <v>584312</v>
       </c>
       <c r="R24" t="n">
-        <v>6869561</v>
+        <v>6869573</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113682668</v>
+        <v>113682664</v>
       </c>
       <c r="B25" t="n">
-        <v>99125</v>
+        <v>99195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3264,7 +3146,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>420</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3281,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584361</v>
+        <v>584320</v>
       </c>
       <c r="R25" t="n">
-        <v>6869501</v>
+        <v>6869565</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3353,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113682669</v>
+        <v>113682665</v>
       </c>
       <c r="B26" t="n">
-        <v>99125</v>
+        <v>99195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3383,7 +3265,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3396,14 +3278,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storåsen, Hls</t>
+          <t>Bläckmyran, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584443</v>
+        <v>584312</v>
       </c>
       <c r="R26" t="n">
-        <v>6869552</v>
+        <v>6869550</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3472,10 +3354,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113682667</v>
+        <v>113682666</v>
       </c>
       <c r="B27" t="n">
-        <v>99125</v>
+        <v>99195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3502,7 +3384,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3519,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584375</v>
+        <v>584368</v>
       </c>
       <c r="R27" t="n">
-        <v>6869525</v>
+        <v>6869558</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3591,10 +3473,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113682623</v>
+        <v>113682667</v>
       </c>
       <c r="B28" t="n">
-        <v>99125</v>
+        <v>99195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3503,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3638,10 +3520,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584365</v>
+        <v>584375</v>
       </c>
       <c r="R28" t="n">
-        <v>6869805</v>
+        <v>6869525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3668,12 +3550,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,10 +3592,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113682666</v>
+        <v>113682668</v>
       </c>
       <c r="B29" t="n">
-        <v>99125</v>
+        <v>99195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3740,7 +3622,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3757,10 +3639,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584368</v>
+        <v>584361</v>
       </c>
       <c r="R29" t="n">
-        <v>6869558</v>
+        <v>6869501</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3829,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113682664</v>
+        <v>113682669</v>
       </c>
       <c r="B30" t="n">
-        <v>99125</v>
+        <v>99195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3859,7 +3741,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3872,14 +3754,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bläckmyran, Hls</t>
+          <t>Storåsen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584320</v>
+        <v>584443</v>
       </c>
       <c r="R30" t="n">
-        <v>6869565</v>
+        <v>6869552</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3941,6 +3823,125 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>113682670</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>584443</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6869561</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
